--- a/excel/train_endurance.xlsx
+++ b/excel/train_endurance.xlsx
@@ -485,12 +485,12 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>74.92130279541016</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>71.43950653076172</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +545,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>70.27890014648438</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="27">
@@ -635,7 +635,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>78.91676330566406</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="45">
@@ -800,7 +800,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>70.85920715332031</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="78">
@@ -845,7 +845,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>73.18040466308594</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="87">
@@ -870,7 +870,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>76.66220855712891</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="92">
@@ -915,7 +915,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>73.76071166992188</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="101">
@@ -1095,7 +1095,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>78.33815002441406</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="137">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>77.24250793457031</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="166">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>77.80426788330078</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="173">
@@ -1295,7 +1295,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>69.6986083984375</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="177">
@@ -1325,7 +1325,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>72.60010528564453</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="183">
